--- a/samples/ss_kediri12_ingest.xlsx
+++ b/samples/ss_kediri12_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,35 +806,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>4x60 MVA + 50 MVAR (bay 5 = MBL)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -883,23 +854,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>injeksi 150 kV Kediri</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -915,7 +879,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -944,23 +907,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>T/L bay Kediri single phi</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -976,7 +932,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1005,23 +960,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>150 kV Kertosono</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1037,7 +985,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1066,35 +1013,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>60 MVA (bay 6,7,8,9) + 50 MVAR</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1123,35 +1061,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>60/30/60 MVA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1198,31 +1127,26 @@
       <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>2x100 MVA (unit 1,4)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1251,23 +1175,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>10 MVAR</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1283,7 +1200,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1312,23 +1228,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>30/30/30 MVA</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1344,7 +1253,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1373,23 +1281,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>single busbar; 30/30/30 MVA</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1405,7 +1306,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1434,35 +1334,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>30/20/30 MVA</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1491,23 +1382,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>ujung subsistem; drop tegangan</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1523,7 +1407,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1630,7 +1513,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Ngoro - Kediri</t>
@@ -1651,7 +1533,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1665,8 +1546,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1683,7 +1562,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1714,7 +1592,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1728,8 +1605,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1746,7 +1621,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1777,7 +1651,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1791,8 +1664,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1809,7 +1680,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1840,7 +1710,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -1854,8 +1723,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1872,13 +1739,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Ngoro - Sukorejo</t>
@@ -1899,7 +1764,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1913,8 +1777,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1931,13 +1793,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Sukorejo - Mojoagung</t>
@@ -1958,7 +1818,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1972,8 +1831,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1990,7 +1847,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2021,7 +1877,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -2035,8 +1890,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2053,7 +1906,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2084,7 +1936,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2098,8 +1949,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2116,13 +1965,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kertosono - Ploso</t>
@@ -2143,7 +1990,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2157,8 +2003,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2175,7 +2019,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2206,7 +2049,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2220,8 +2062,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2238,7 +2078,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2307,7 +2146,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Beban IBT Kediriberbeban lebih60% sehingga tidakmemenuhiN-1</t>
+          <t>[N-1] Beban IBT Kediri berbeban lebih 60% sehingga tidak memenuhiN-1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2317,12 +2156,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT Kediri 1,2 dengan total target sebesar336MW. (Berdasark an Deklarasi ROB Mei 2026). 2. Pekerjaan IBT tidak boleh berbarengan dengan pekerjaan di SS Surabaya barat dan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Kediri 1,2 dengan total target sebesar 336MW. (Berdasark an Deklarasi ROB Mei 2026). 2. Pekerjaan IBT tidak boleh berbarengan dengan pekerjaan di SS Surabaya barat dan saat beban rendah</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2027). Jangka Menengah : 2. Pembangunan PLTB 150 kV Total 200 MW Tahap I di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 3. Pembangunan PLTB 150 kV Total 200 MW Tahap II di Usulan / Solusi Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 4. Pembangunan PLTP Gunung Pandandan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD 2033)</t>
+          <t>Jangka Pendek: 1. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah : 2. Pembangunan PLTB 150 kV Total 200 MW Tahap I di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 3. Pembangunan PLTB 150 kV Total 200 MW Tahap II di Usulan / Solusi Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 4. Pembangunan PLTP Gunung Pandandan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD 2033)</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2181,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan pada SUTT 150 kV Kediri- Jayakertas dan Kediri-Kertosono sudah berbeban diatas 60% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan pada SUTT 150 kV Kediri- Jayakertas dan Kediri-Kertosono sudah berbeban diatas 60% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2357,7 +2196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kVBanaran- MojoagungmenjadiSUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026 (update: estimasi COD 2028)). 2. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2027).. Jangka Menegah : 3. Rekonduktoring SUTT 150 kV Kediri - Jayakertas - Kertosono. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 4. Pembangunan PLTB 150 kV Total 200 MW Tahap I di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 5. Pembangunan PLTP Gunung Pandan dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 6. Pembangunan PLTB 150 kV Total 200 MW Tahap II di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kV Banaran- Mojoagung menjadi SUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026 (update: estimasi COD 2028)). 2. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027).. Jangka Menegah : 3. Rekonduktoring SUTT 150 kV Kediri - Jayakertas - Kertosono. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 4. Pembangunan PLTB 150 kV Total 200 MW Tahap I di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 5. Pembangunan PLTP Gunung Pandan dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 6. Pembangunan PLTB 150 kV Total 200 MW Tahap II di Jombang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2231,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kVBanaran- MojoagungmenjadiSUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 Usulan / Solusi - 2034, COD Tahun 2026 (update: est COD 2028)). 2. Normalisasi Doble phi SUTT 150 kV Kediri - Jayakertas - Kertosono. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2027</t>
+          <t>Jangka Pendek : 1. Percepatan Rekonfigurasi dan Rerouting SUTT 150 kV Banaran- Mojoagung menjadi SUTT 150 kV Kediri-Mojoagung. (Berdasarkan RUPTL 2025 Usulan / Solusi - 2034, COD Tahun 2026 (update: est COD 2028)). 2. Normalisasi Doble phi SUTT 150 kV Kediri - Jayakertas - Kertosono. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2261,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sudah terpasang OLS di SUTT Kertosono-Nganjuk 1,2 dengan total target sebesar34 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
+          <t>Sudah terpasang OLS di SUTT Kertosono -Nganjuk 1,2 dengan total target sebesar 34 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2482,12 +2321,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di ujungSubsistem Kediri 1,2</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di ujung Subsistem Kediri 1,2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drop tegangan yang cukup signifikan di SubsistemKediri 1,2</t>
+          <t>Drop tegangan yang cukup signifikan di Subsistem Kediri 1,2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2497,7 +2336,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Usulan Pemasangan Kapasitor di GI Jombang (50 MVAR), usulan COD Tahun 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F330000 00/2024 tanggal 22 Mei 2024. 2. Usulan Pemasangan Kapasitor di GI New Wlingi II (50 MVAR)saat SUTT 150 kV New Wlingi - PLTA Wlingi Beroprasi, usulan</t>
+          <t>Jangka Pendek : 1. Usulan Pemasangan Kapasitor di GI Jombang (50 MVAR), usulan COD Tahun 2026 (Surat UIP2B Jamali No. 2153/REN.00.01/F330000 00/2024 tanggal 22 Mei 2024. 2. Usulan Pemasangan Kapasitor di GI New Wlingi II (50 MVAR) saat SUTT 150 kV New Wlingi - PLTA Wlingi Beroprasi, usulan</t>
         </is>
       </c>
     </row>
